--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_08-05-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_08-05-2026.xlsx
@@ -2428,7 +2428,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>£70.18</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
